--- a/ProductionPlan_20260426.xlsx
+++ b/ProductionPlan_20260426.xlsx
@@ -44,7 +44,7 @@
     <t>2.3%</t>
   </si>
   <si>
-    <t>17:09</t>
+    <t>02:43</t>
   </si>
   <si>
     <t>BBJ</t>
